--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/20 11:34:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>240000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29524.24</t>
+          <t>240000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29524.24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29524.24</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19524.24</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>240000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29524.24</t>
+          <t>440000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53620.63</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>19524.24</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>43620.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>53620.63</t>
+          <t>440000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53620.63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10888</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>43620.63</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>42732.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>53620.63</t>
+          <t>440000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>53620.63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>42732.63</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>42544.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,83 +340,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>53620.63</t>
+          <t>440000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>53620.63</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>31076</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>42544.63</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22544.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,12 +340,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -367,83 +367,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>53620.63</t>
+          <t>440000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>53620.63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>32076</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>22544.63</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21544.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15 10:26:38</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20987.65</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -198,154 +198,184 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09/15 10:26:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20987.65</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>suchen668</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -355,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -367,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -382,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -394,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 11:34:21</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -418,59 +448,140 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>09/20 11:57:04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>09/20 11:34:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>440000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>53620.63</t>
-        </is>
-      </c>
-    </row>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>32076</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>770000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>94938.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>32364</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21544.63</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>62574.31</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -466,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -478,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -505,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>770000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>94938.31</t>
+          <t>940000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>116188.31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>32364</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>62574.31</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>83824.31</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,83 +562,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>940000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>116188.31</t>
+          <t>1200000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>149099.7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>32364</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>83824.31</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>116735.7</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,83 +604,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>149099.7</t>
+          <t>1300000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>161599.7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>32364</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>116735.7</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>129235.7</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,83 +631,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>161599.7</t>
+          <t>1300000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>161599.7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>44864</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>129235.7</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>116735.7</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,83 +673,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>161599.7</t>
+          <t>1450000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>180467.63</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>44864</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>116735.7</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>135603.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,83 +700,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1450000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>180467.63</t>
+          <t>1450000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>180467.63</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>63731</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>135603.63</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>116736.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -634,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -688,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1450000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>180467.63</t>
+          <t>1550000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>193125.86</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>63731</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>116736.63</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>129394.86</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,83 +769,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1550000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>193125.86</t>
+          <t>1550000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>193125.86</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>76389</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>129394.86</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>116736.86</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -757,7 +772,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,83 +811,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1550000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>193125.86</t>
+          <t>1650000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>76389</t>
+          <t>205247.07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>76389</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>116736.86</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>128858.07</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,83 +838,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1650000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>205247.07</t>
+          <t>1650000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>76389</t>
+          <t>205247.07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>88510</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>128858.07</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>116737.07</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -691,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +760,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -799,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -826,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,83 +880,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1650000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>205247.07</t>
+          <t>1950000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>242284.11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>88510</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>116737.07</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>153774.11</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>10/07 13:40:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,83 +907,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1950000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>242284.11</t>
+          <t>1950000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>242284.11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>125497</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>153774.11</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>116787.11</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 12:39:04</t>
+          <t>10/14 10:48:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>28025.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/21 11:54:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>35220.13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>tiaowu7888</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:56:39</t>
+          <t>09/20 17:33:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
+          <t>09/20 11:56:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/20 11:34:05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/15 10:26:38</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/07 13:40:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>10/07 13:40:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -760,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>09/20 17:33:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>suchen668</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +883,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -895,7 +910,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,83 +949,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1950000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>242284.11</t>
+          <t>2170000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>125497</t>
+          <t>270309.58</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>125497</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>116787.11</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>144812.58</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/14 10:48:20</t>
+          <t>10/23 10:38:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/07 12:39:04</t>
+          <t>10/15 11:33:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/14 10:48:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>28025.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 11:54:07</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiaowu7888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 17:33:17</t>
+          <t>09/23 13:35:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -492,129 +492,53 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09/20 11:56:39</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>24096.39</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>xiaoshuai5688</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 11:34:05</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>8536.59</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>xiaoshuai5688</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15 10:26:38</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20987.65</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -622,7 +546,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
@@ -639,79 +563,110 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10/07 13:40:42</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>36987</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>10/06 11:58:58</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/07 13:40:42</t>
+          <t>09/30 19:09:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -721,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -733,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>09/29 12:36:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -748,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -757,302 +712,59 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10/01 15:53:56</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>12658</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>18867</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/29 12:36:05</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12500</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
+          <t>1750000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/20 17:33:40</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>USDT16889888</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
+          <t>218505.87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/20 12:16:10</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>suchen668</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
+          <t>93133</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>09/20 11:57:04</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>xiaoshuai5688</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>09/20 11:56:54</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>xiaoshuai5688</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>09/20 11:34:21</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2170000</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>270309.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>125497</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>144812.58</t>
+          <t>125372.87</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/07 13:40:42</t>
+          <t>10/23 10:38:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>10/07 13:40:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,83 +688,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>09/30 19:09:56</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>09/29 12:36:05</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>12500</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1750000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>218505.87</t>
+          <t>1750000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93133</t>
+          <t>218505.87</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>93321</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>125372.87</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>125184.87</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/23 10:38:36</t>
+          <t>10/23 13:23:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/07 13:40:42</t>
+          <t>10/23 10:38:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>10/07 13:40:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,83 +715,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/30 19:09:56</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>09/29 12:36:05</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>12500</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1750000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>218505.87</t>
+          <t>1750000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>218505.87</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>94321</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>125184.87</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>124184.87</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/23 10:38:30</t>
+          <t>10/27 10:15:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 11:33:56</t>
+          <t>10/23 10:38:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/14 10:48:20</t>
+          <t>10/15 11:33:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/07 12:39:04</t>
+          <t>10/14 10:48:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>28025.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 13:35:54</t>
+          <t>09/28 14:39:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>32911.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1750000</t>
+          <t>1630000</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>218505.87</t>
+          <t>203353.43</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>124184.87</t>
+          <t>109032.43</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/23 13:23:39</t>
+          <t>10/27 10:15:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/23 10:38:36</t>
+          <t>10/23 13:23:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/07 13:40:42</t>
+          <t>10/23 10:38:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/06 11:58:58</t>
+          <t>10/07 13:40:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10/01 15:53:56</t>
+          <t>10/06 11:58:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/30 19:09:56</t>
+          <t>10/01 15:53:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>09/30 19:09:56</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>09/29 12:36:05</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>12500</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>203353.43</t>
+          <t>1630000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>94321</t>
+          <t>203353.43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>94509</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>109032.43</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>108844.43</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 10:15:34</t>
+          <t>10/30 09:55:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>15189.87</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/23 10:38:30</t>
+          <t>10/27 10:15:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/15 11:33:56</t>
+          <t>10/23 10:38:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/14 10:48:20</t>
+          <t>10/15 11:33:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/07 12:39:04</t>
+          <t>10/14 10:48:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>28025.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1630000</t>
+          <t>1490000</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>203353.43</t>
+          <t>185631.91</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>108844.43</t>
+          <t>91122.91</t>
         </is>
       </c>
     </row>
